--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_fruit.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_fruit.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\qiji\tszz_GMTest\engine_package\Res\MuDataEditor\天使之战_v1.0.0.0\Out\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40184970-3CD6-429E-9158-442A4AF083C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5B68C4F-C65B-464E-B96C-DC5EC45DD479}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
